--- a/data/output/all_in主动基金风控纪律手册.xlsx
+++ b/data/output/all_in主动基金风控纪律手册.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Finance\alpha_fund_check\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{936FF1F6-EEAF-49DD-A8B8-F6CB5833A084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9E73F1-EF38-4698-9019-C418C1E870EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总览" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,25 @@
     <sheet name="数据口径与纪律" sheetId="5" r:id="rId5"/>
     <sheet name="季度检查表" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="321">
   <si>
     <t>执行记录表：触发必须记录；规则触发当天不得修改阈值</t>
   </si>
@@ -982,6 +995,119 @@
   </si>
   <si>
     <t>2026Q2</t>
+  </si>
+  <si>
+    <t>季报结论</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>季报偏积极，但风格集中度进一步提高，已经明显是一只</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>算力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>国产科技链</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的高弹性基金，不再是传统意义上的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>均衡中小盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -993,7 +1119,7 @@
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="0%;[Red]\(0%\)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1049,6 +1175,23 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1172,7 +1315,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1261,6 +1404,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="9" fillId="12" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="9" fillId="12" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="9" fillId="12" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1274,11 +1422,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="9" fillId="12" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="9" fillId="12" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="9" fillId="12" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1586,16 +1730,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
       <c r="I1" s="29"/>
       <c r="J1" s="29"/>
       <c r="K1" s="29"/>
@@ -1605,16 +1749,16 @@
       <c r="O1" s="29"/>
     </row>
     <row r="2" spans="1:15" ht="44" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:15" ht="38" customHeight="1"/>
     <row r="4" spans="1:15" ht="38" customHeight="1">
@@ -1624,12 +1768,12 @@
       <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="1:15" ht="38" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -1740,16 +1884,16 @@
     <row r="13" spans="1:15" ht="38" customHeight="1"/>
     <row r="14" spans="1:15" ht="38" customHeight="1"/>
     <row r="15" spans="1:15" ht="38" customHeight="1">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
     </row>
     <row r="16" spans="1:15" ht="38" customHeight="1">
       <c r="A16" s="3" t="s">
@@ -2538,21 +2682,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="48" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
       <c r="N1" s="29"/>
       <c r="O1" s="29"/>
     </row>
@@ -2904,7 +3048,7 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="15.8125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="8" width="12" customWidth="1"/>
@@ -2913,18 +3057,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
       <c r="K1" s="29"/>
       <c r="L1" s="29"/>
       <c r="M1" s="29"/>
@@ -2969,198 +3113,198 @@
       <c r="I3" s="15"/>
     </row>
     <row r="4" spans="1:15" ht="38" customHeight="1">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="40"/>
-      <c r="H4" s="37" t="s">
+      <c r="G4" s="35"/>
+      <c r="H4" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="41"/>
-      <c r="J4" s="38"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="33"/>
     </row>
     <row r="5" spans="1:15" ht="38" customHeight="1">
-      <c r="A5" s="39"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="38"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="33"/>
     </row>
     <row r="6" spans="1:15" ht="38" customHeight="1">
-      <c r="A6" s="39"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="38"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="33"/>
     </row>
     <row r="7" spans="1:15" ht="38" customHeight="1">
-      <c r="A7" s="39"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="38"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="33"/>
     </row>
     <row r="8" spans="1:15" ht="38" customHeight="1">
-      <c r="A8" s="39"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="38"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="33"/>
     </row>
     <row r="9" spans="1:15" ht="38" customHeight="1">
-      <c r="A9" s="39"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="38"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="33"/>
     </row>
     <row r="10" spans="1:15" ht="38" customHeight="1">
-      <c r="A10" s="39"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="38"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="33"/>
     </row>
     <row r="11" spans="1:15" ht="38" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="38"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="33"/>
     </row>
     <row r="12" spans="1:15" ht="38" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="38"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="33"/>
     </row>
     <row r="13" spans="1:15" ht="38" customHeight="1">
-      <c r="A13" s="39"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="38"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="33"/>
     </row>
     <row r="14" spans="1:15" ht="38" customHeight="1">
-      <c r="A14" s="39"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="38"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="33"/>
     </row>
     <row r="15" spans="1:15" ht="38" customHeight="1">
-      <c r="A15" s="39"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="38"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="33"/>
     </row>
     <row r="16" spans="1:15" ht="38" customHeight="1">
-      <c r="A16" s="39"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="38"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="33"/>
     </row>
     <row r="17" spans="1:10" ht="38" customHeight="1">
-      <c r="A17" s="39"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="38"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="33"/>
     </row>
     <row r="18" spans="1:10" ht="38" customHeight="1">
-      <c r="A18" s="39"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="38"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="33"/>
     </row>
     <row r="19" spans="1:10" ht="38" customHeight="1"/>
     <row r="20" spans="1:10" ht="38" customHeight="1"/>
@@ -3215,16 +3359,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="50" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
       <c r="I1" s="29"/>
       <c r="J1" s="29"/>
       <c r="K1" s="29"/>
@@ -3429,16 +3573,16 @@
     </row>
     <row r="14" spans="1:15" ht="50" customHeight="1"/>
     <row r="15" spans="1:15" ht="50" customHeight="1">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
     </row>
     <row r="16" spans="1:15" ht="50" customHeight="1">
       <c r="A16" s="3" t="s">
@@ -3540,13 +3684,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>283</v>
       </c>
@@ -3593,7 +3737,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>298</v>
       </c>
@@ -3639,8 +3783,11 @@
       <c r="O2" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="C3" t="s">
         <v>313</v>
       </c>
@@ -3660,7 +3807,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:16">
       <c r="C4" t="s">
         <v>313</v>
       </c>
@@ -3680,7 +3827,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="C5" t="s">
         <v>313</v>
       </c>
@@ -3700,7 +3847,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="C6" t="s">
         <v>313</v>
       </c>
@@ -3720,7 +3867,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="C7" t="s">
         <v>313</v>
       </c>
@@ -3740,7 +3887,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="C8" t="s">
         <v>313</v>
       </c>
@@ -3760,7 +3907,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="C9" t="s">
         <v>313</v>
       </c>
@@ -3780,7 +3927,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="C10" t="s">
         <v>313</v>
       </c>
@@ -3800,7 +3947,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="C11" t="s">
         <v>313</v>
       </c>
@@ -3820,7 +3967,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="C12" t="s">
         <v>313</v>
       </c>
@@ -3840,7 +3987,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="C13" t="s">
         <v>313</v>
       </c>
@@ -3860,7 +4007,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="C14" t="s">
         <v>313</v>
       </c>
@@ -3880,12 +4027,12 @@
         <v>314</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:16" ht="15">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -3931,8 +4078,11 @@
       <c r="O17" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="P17" s="42" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
         <v>11</v>
       </c>
